--- a/backend/Toast Switchover Dates.xlsx
+++ b/backend/Toast Switchover Dates.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -463,6 +463,16 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>00a73b16-9303-4e59-b248-bc320ffc4342</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>One row per store. Switchover Date = the first day Toast was the POS at that location.</t>
@@ -470,6 +480,16 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9fc3101b-8b55-4fbc-b6cb-195813efc0a1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Format: YYYY-MM-DD (Excel date format also accepted).</t>
@@ -477,9 +497,1123 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>d93f2ed0-12b9-42c7-9b77-3ac92e6415fd</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Re-import after edits: cd backend &amp;&amp; venv/bin/python import_switchover_dates.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>347e7817-21da-472a-b678-40f3790e6a1a</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6863fa94-0d1e-4bfe-91dd-c0f239797ad8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0ed74899-f247-4d4f-9b60-84a7b3c50f60</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>61cf23aa-ecb0-4c87-9bc1-9adb271a6f89</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>a1e17ab4-c5a4-426f-b211-8f297e0db88c</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>18d3a03d-9c6a-40b5-a74c-2ce346e3d5ef</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>e8484606-af17-4cfc-bd0f-91b01ee60fd9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>f05b840b-b9c7-4c17-8ba7-bc1bb2884aed</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3add7aff-d2fc-4ff7-8c1d-2bf86d5c7aca</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>b0a73c6b-b1cb-4baf-98cd-a8031ebf4a49</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>380abc44-7e1e-46b8-a922-78bf99017abe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>b714f540-553e-4bef-9fe6-28f21e70770e</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>694ce676-4fca-44c0-ba3d-409c6900ad9d</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0b30cc76-c644-4b63-bec8-bf9ffa199377</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>25d48919-fad3-4329-9aac-d5d96515a2c2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>9b4eb686-c998-4d7d-aa8f-2f2dc022dc9f</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3fd6f4d3-4a8d-497a-98d1-c4fe8103044f</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>63b9d37d-a0b0-4fbb-9de4-cc133d15acbc</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>005ed493-b309-4c54-a50d-75d47383ad9b</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>70ba606a-bb0a-445d-818f-8d30260e9c57</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a0b2a3c5-74fc-4ad1-a711-6d8a64be3007</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>afa120ac-647d-4bd7-8b83-b4d7112b96aa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>da88e78a-3f47-4baf-ba76-3e5a7e925d6c</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>38c5fc36-9554-426c-b433-6bea616b0a5f</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>47b4ea54-2c25-4f40-9f1d-9b2f4e25708e</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5e8b9e62-c74e-4a3b-ac90-8e3cdfc1171a</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>571e325a-0ab2-44ad-a6cc-db540ad6113b</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6c4c987c-4e1d-4d47-93ab-fc9782bb9a3c</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8b5f3e1b-5a92-4ca9-b893-40c36e5e4f62</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>e36bbc2a-fde8-4ca1-bcc2-01f6ba8092bb</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>005d4f3b-715e-4b77-88e8-09c2d1ed3a89</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>b52c8d0f-81fd-4c99-bd10-6fa901348ace</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9052f94f-59c5-4265-999b-575d4fe41310</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9e8f983a-dcc8-404c-9b03-d2ff11e41365</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>a70f7d7c-827a-44af-9dab-4e7d9c9d976e</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>f3c437d1-07c2-42bb-9b48-77e29d09c4fe</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>b34e0c22-9e08-4358-aacf-4784729b4774</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15f1aaf8-a6c3-4354-bad6-63785961fd71</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>c19b1d75-9037-400e-bd6d-341116070af2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4353ef74-9651-4a2e-8379-51cef5b7a96a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1f8d20e0-dc30-471e-9096-c8dfa4295e9d</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>af1eefaf-9dc0-4d82-8faa-b8cfc92d4b2a</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cdef84d3-5c6d-4c1f-b10d-d5798842be12</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ae2c3942-483a-45d2-a775-74edfa3fd4ee</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>be38b1c3-89dd-43d7-86f0-611eb0333438</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>c65f8836-4a00-45ce-a861-a3a1ddff34b3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>295f5b13-0ea3-4a32-9f25-399995c8724a</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3a5bb077-3866-4d86-aa53-78b12a84bbf6</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>e1c1e1ee-c2b1-47fa-bf42-95de0d7fa9b2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>e54f0079-5c7c-44e1-a054-ced2ebbff036</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3340a83a-6fc6-4542-962b-d4f873437099</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>62fd2c58-220b-48d0-88d3-37542ad59e81</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>183e438f-9915-456d-a926-0b26d2c0d381</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>54c7fd7a-0522-40c9-9f59-af3f98f72cec</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6a776ceb-aac6-468a-9c27-9e99eeb0cd22</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ac9a34be-24a0-4470-b4e6-be35140153a1</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9a508480-3c7e-4c44-b576-e0ecb6594f4e</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>6a6c7ca4-0ad5-4b2a-afc9-662e9f335ae7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8b421062-6a5e-43e4-aca8-3f379e198c5e</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>d604905c-aa66-46ad-b418-5ab4ee88e42f</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>142874c0-307f-41de-9493-d9919fd11215</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>123f2fa1-08a5-484e-9b98-9b76095ffdba</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>12da99f3-dbaa-47d4-aca3-d2781188d76e</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>577ac58c-9834-4c4e-a6b9-8d0e8266e18d</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>d9577cb4-2d5a-4b52-9de0-4043f2265b8a</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>c78ed07c-1b80-4416-878c-2308862fbe50</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>48c02d33-a0a2-4f3d-9112-4fe11144c79d</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>a7cccaa8-7c1c-4f46-b76f-7987e6e3cc2f</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>580e0c1b-5489-415f-a609-b52991bf1df0</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1970cf05-2866-4ea4-a4ac-266b36816fce</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ee7af43e-a9e1-412e-90fb-9b9880d3fa0c</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>5c82bb84-92b4-4907-8950-fc29582dbeb4</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>88f6c21f-1f05-41f0-8dc9-56ee6a7a2205</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>b42b1def-510f-42b1-a0c4-2947fda858a8</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ce32dcb6-0cd6-48af-9651-1314544bfb3a</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1d8180bd-90fc-4efb-870e-125a03aecae8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7ba61337-a059-4ab3-8f5a-8c2defbdf9e7</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>a8687e40-640e-4d86-bae5-2a684cb8c4c3</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>bb6fedb9-dd3b-4541-9f60-b77198f6d67e</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>f69d5d97-1e66-40f4-a0da-316083193c46</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1f1dcbf7-825a-4cb0-9289-0dfed05eedb7</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>3d4eb896-d47b-45f4-b0a5-81e78480b018</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>18dca8e0-5a1d-4a69-951e-e124cf1266d1</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>494119f6-f7d1-4304-8a62-63303aa742a1</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>8d61082d-da30-40d8-915d-2a83dc5b0ec5</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>d7ab920e-b4bc-4245-97cb-b749db37dccd</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4f092f7c-70ec-4293-bda6-8b743eceff6c</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>07a31b62-d025-4da8-b296-2e7181abfcdc</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>c793e331-e3fc-464c-87d1-03312e82535a</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>49e583cc-3bec-4259-9901-970c63decfae</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>a368ce14-2147-48bd-aedd-9936c80245ac</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>adc6b102-adf8-4fa8-ba06-7e3916eaad3a</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
